--- a/notes/LIBELLULA(diario).xlsx
+++ b/notes/LIBELLULA(diario).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0037e56ddff3a368/Desktop/Libellula/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel\OneDrive\Desktop\Libellula\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{1A320F2B-9005-4399-9E48-5F210EFD5E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8882A9F2-4122-40AF-B656-076DAC16F7FC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABF8704-F42D-4ADD-B462-98794C3F457C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{CC99F97F-3E72-4FEA-AA64-B39819E65309}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>PLANEJAMENTO LIBELLULA (secreto)</t>
   </si>
@@ -154,7 +154,22 @@
     <t>Sexta-feira, 20/02/26</t>
   </si>
   <si>
-    <t>16h31-</t>
+    <t>16h31-indeterminado</t>
+  </si>
+  <si>
+    <t>1) EXTRAORDINÁRIO PROGRESSO! Constuir um EPF com 93% de eficiência! NEM O CHATGPT ACREDITOU!</t>
+  </si>
+  <si>
+    <t>1) Terminei o EPF! Ele está tão bom que nem dá pra acreditar! Criei uma rotina para descobrir qual indicador econômico influiu mais na eficiencia do EPF, e foi o oscilador estocástico rápido de 10 períodos (%K10)</t>
+  </si>
+  <si>
+    <t>NEM ME LEMBRO DE NADA DO QUE ACONTECEU NESSE DIA!</t>
+  </si>
+  <si>
+    <t>Domingo, 22/02/26</t>
+  </si>
+  <si>
+    <t>Indeterminado-indeterminado</t>
   </si>
 </sst>
 </file>
@@ -257,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -307,6 +322,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -646,8 +667,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A98371-216A-4D1C-8D7B-786B21A1BFEF}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="99.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="120" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12.7109375" style="10" customWidth="1"/>
     <col min="3" max="3" width="30.7109375" style="2" customWidth="1"/>
@@ -718,7 +739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
@@ -744,7 +765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
@@ -770,7 +791,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>28</v>
       </c>
@@ -796,12 +817,31 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="14" t="s">
         <v>30</v>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="E8" s="12"/>
+      <c r="H8" s="24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
